--- a/order_forms/044_pod_submission_form--order_forms.xlsx
+++ b/order_forms/044_pod_submission_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'t-shirt',_'value':_'t-shirt'}</t>
+          <t>t-shirt</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'T-shirt', 'value': 'T-shirt'}</t>
+          <t>T-shirt</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mug',_'value':_'mug'}</t>
+          <t>mug</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mug', 'value': 'Mug'}</t>
+          <t>Mug</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'s',_'value':_'s'}</t>
+          <t>s</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'S', 'value': 'S'}</t>
+          <t>S</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'m',_'value':_'m'}</t>
+          <t>m</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'M', 'value': 'M'}</t>
+          <t>M</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'l',_'value':_'l'}</t>
+          <t>l</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'L', 'value': 'L'}</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'xl',_'value':_'xl'}</t>
+          <t>xl</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'XL', 'value': 'XL'}</t>
+          <t>XL</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'yes'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': 'Yes'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'no'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': 'No'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
